--- a/content/cv/AllConferences_Seminar_Presentation_Summary.xlsx
+++ b/content/cv/AllConferences_Seminar_Presentation_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boris/Documents/WORK/CODE/GitHub/boriswebsite/content/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43002D92-9F3C-FE44-97C0-C1A1212AF6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723F67A2-6F32-9141-8526-96986F1D1798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="252">
   <si>
     <t>Conf</t>
   </si>
@@ -788,6 +788,12 @@
   </si>
   <si>
     <t>Building &amp; Evaluating Transcriptomic Surrogate Markers as Correlates of Vaccination</t>
+  </si>
+  <si>
+    <t>Utilising correlates of protection to accelerate vaccine development</t>
+  </si>
+  <si>
+    <t>https://events.wellcome.org/event/fd74910d-822c-4d15-9b5c-115fc8a1070a/home-page</t>
   </si>
 </sst>
 </file>
@@ -905,7 +911,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -958,34 +964,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1295,163 +1283,165 @@
     <col min="17" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28" t="s">
+    <row r="1" spans="1:18" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" s="28" t="s">
+      <c r="Q1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="R1" s="25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="32" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="12">
         <v>2026</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="30">
-        <v>0</v>
-      </c>
-      <c r="F2" s="30">
-        <v>0</v>
-      </c>
-      <c r="G2" s="30">
-        <v>1</v>
-      </c>
-      <c r="H2" s="30">
-        <v>0</v>
-      </c>
-      <c r="I2" s="30">
-        <v>1</v>
-      </c>
-      <c r="J2" s="30">
-        <v>1</v>
-      </c>
-      <c r="K2" s="30">
-        <v>1</v>
-      </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="31" t="s">
+      <c r="E2" s="12">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0</v>
+      </c>
+      <c r="I2" s="12">
+        <v>1</v>
+      </c>
+      <c r="J2" s="12">
+        <v>1</v>
+      </c>
+      <c r="K2" s="12">
+        <v>1</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="22">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="22">
+        <v>0</v>
+      </c>
+      <c r="F3" s="22">
+        <v>0</v>
+      </c>
+      <c r="G3" s="22">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22">
+        <v>0</v>
+      </c>
+      <c r="I3" s="22">
+        <v>1</v>
+      </c>
+      <c r="J3" s="22">
+        <v>1</v>
+      </c>
+      <c r="K3" s="22">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="N2" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="26">
-        <v>2026</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="26">
-        <v>0</v>
-      </c>
-      <c r="F3" s="26">
-        <v>0</v>
-      </c>
-      <c r="G3" s="26">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26">
-        <v>0</v>
-      </c>
-      <c r="I3" s="26">
-        <v>1</v>
-      </c>
-      <c r="J3" s="26">
-        <v>1</v>
-      </c>
-      <c r="K3" s="26">
-        <v>1</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="24" t="s">
+      <c r="R3" s="13" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1489,7 +1479,7 @@
       <c r="K4" s="22">
         <v>1</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="24" t="s">
         <v>239</v>
       </c>
       <c r="M4" s="3" t="s">
@@ -1504,7 +1494,7 @@
       <c r="P4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="22" t="s">
+      <c r="R4" s="13" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3929,6 +3919,7 @@
     <hyperlink ref="L18" r:id="rId10" xr:uid="{1665FC53-74DA-2C45-82E3-FF20918BA164}"/>
     <hyperlink ref="L4" r:id="rId11" xr:uid="{CD2FE44B-DA38-7048-B009-A6AFC4D989E2}"/>
     <hyperlink ref="L3" r:id="rId12" xr:uid="{4E7545E0-4FDE-5F44-8CF3-F958E5EBED07}"/>
+    <hyperlink ref="L2" r:id="rId13" xr:uid="{993256A8-0873-D94D-8B4B-FB0F611DC67C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/content/cv/AllConferences_Seminar_Presentation_Summary.xlsx
+++ b/content/cv/AllConferences_Seminar_Presentation_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boris/Documents/WORK/CODE/GitHub/boriswebsite/content/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723F67A2-6F32-9141-8526-96986F1D1798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8D1DC5-E1DE-7F4A-AB64-EF1DAFE4EB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -787,13 +787,13 @@
     <t>MUSiCC</t>
   </si>
   <si>
-    <t>Building &amp; Evaluating Transcriptomic Surrogate Markers as Correlates of Vaccination</t>
-  </si>
-  <si>
     <t>Utilising correlates of protection to accelerate vaccine development</t>
   </si>
   <si>
     <t>https://events.wellcome.org/event/fd74910d-822c-4d15-9b5c-115fc8a1070a/home-page</t>
+  </si>
+  <si>
+    <t>Building \&amp; Evaluating Transcriptomic Surrogate Markers as Correlates of Vaccination</t>
   </si>
 </sst>
 </file>
@@ -1374,16 +1374,16 @@
         <v>1</v>
       </c>
       <c r="L2" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>247</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>44</v>
